--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123068275</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123080637</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123068275</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123080637</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123068275</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123080637</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123068275</v>
+        <v>123080637</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566041</v>
+        <v>566045</v>
       </c>
       <c r="R2" t="n">
-        <v>6583297</v>
+        <v>6583328</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123080637</v>
+        <v>123068275</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -862,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566045</v>
+        <v>566041</v>
       </c>
       <c r="R3" t="n">
-        <v>6583328</v>
+        <v>6583297</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123068275</v>
+        <v>123080637</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566041</v>
+        <v>566045</v>
       </c>
       <c r="R2" t="n">
-        <v>6583297</v>
+        <v>6583328</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123080637</v>
+        <v>123068275</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -862,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566045</v>
+        <v>566041</v>
       </c>
       <c r="R3" t="n">
-        <v>6583328</v>
+        <v>6583297</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123080637</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>123068275</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123080637</v>
+        <v>123068275</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566045</v>
+        <v>566041</v>
       </c>
       <c r="R2" t="n">
-        <v>6583328</v>
+        <v>6583297</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -815,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123068275</v>
+        <v>123080637</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -850,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -867,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566041</v>
+        <v>566045</v>
       </c>
       <c r="R3" t="n">
-        <v>6583297</v>
+        <v>6583328</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +907,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ett fyrtiotal plantor i mossrik äldre barrskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,144 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126629474</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövlunda, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566040</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6583297</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>U-Kun-0123</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>foto OK</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre barrskog/kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -953,7 +953,7 @@
         <v>126629474</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -953,7 +953,7 @@
         <v>126629474</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1043-2025 artfynd.xlsx
+++ b/artfynd/A 1043-2025 artfynd.xlsx
@@ -953,7 +953,7 @@
         <v>126629474</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
